--- a/Team-Data/2007-08/3-17-2007-08.xlsx
+++ b/Team-Data/2007-08/3-17-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,46 +728,46 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F2" t="n">
         <v>38</v>
       </c>
       <c r="G2" t="n">
-        <v>0.433</v>
+        <v>0.424</v>
       </c>
       <c r="H2" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I2" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="J2" t="n">
-        <v>79.59999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="K2" t="n">
-        <v>0.447</v>
+        <v>0.445</v>
       </c>
       <c r="L2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="M2" t="n">
         <v>12.4</v>
       </c>
       <c r="N2" t="n">
-        <v>0.353</v>
+        <v>0.349</v>
       </c>
       <c r="O2" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="P2" t="n">
-        <v>27</v>
+        <v>27.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.773</v>
+        <v>0.774</v>
       </c>
       <c r="R2" t="n">
         <v>12.4</v>
@@ -712,7 +779,7 @@
         <v>42.5</v>
       </c>
       <c r="U2" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="V2" t="n">
         <v>15.2</v>
@@ -727,19 +794,19 @@
         <v>5.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>96.5</v>
+        <v>96.3</v>
       </c>
       <c r="AC2" t="n">
-        <v>-2.3</v>
+        <v>-2.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE2" t="n">
         <v>19</v>
@@ -754,13 +821,13 @@
         <v>5</v>
       </c>
       <c r="AI2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK2" t="n">
         <v>22</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>20</v>
       </c>
       <c r="AL2" t="n">
         <v>27</v>
@@ -769,10 +836,10 @@
         <v>28</v>
       </c>
       <c r="AN2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AO2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP2" t="n">
         <v>7</v>
@@ -793,7 +860,7 @@
         <v>15</v>
       </c>
       <c r="AV2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW2" t="n">
         <v>14</v>
@@ -802,13 +869,13 @@
         <v>3</v>
       </c>
       <c r="AY2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ2" t="n">
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB2" t="n">
         <v>20</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-17-2007-08</t>
+          <t>2008-03-17</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F3" t="n">
         <v>13</v>
       </c>
       <c r="G3" t="n">
-        <v>0.803</v>
+        <v>0.8</v>
       </c>
       <c r="H3" t="n">
         <v>48.2</v>
@@ -861,28 +928,28 @@
         <v>36.3</v>
       </c>
       <c r="J3" t="n">
-        <v>76.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="K3" t="n">
         <v>0.477</v>
       </c>
       <c r="L3" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="M3" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="N3" t="n">
-        <v>0.384</v>
+        <v>0.385</v>
       </c>
       <c r="O3" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="P3" t="n">
-        <v>26.9</v>
+        <v>27</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.767</v>
+        <v>0.765</v>
       </c>
       <c r="R3" t="n">
         <v>9.800000000000001</v>
@@ -891,10 +958,10 @@
         <v>31.6</v>
       </c>
       <c r="T3" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U3" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="V3" t="n">
         <v>15.2</v>
@@ -912,16 +979,16 @@
         <v>22.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.6</v>
+        <v>100.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -960,16 +1027,16 @@
         <v>8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AR3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS3" t="n">
         <v>9</v>
       </c>
       <c r="AT3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-17-2007-08</t>
+          <t>2008-03-17</t>
         </is>
       </c>
     </row>
@@ -1025,22 +1092,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E4" t="n">
         <v>24</v>
       </c>
       <c r="F4" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>0.358</v>
+        <v>0.364</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>35.6</v>
+        <v>35.7</v>
       </c>
       <c r="J4" t="n">
         <v>80</v>
@@ -1055,19 +1122,19 @@
         <v>17.6</v>
       </c>
       <c r="N4" t="n">
-        <v>0.363</v>
+        <v>0.366</v>
       </c>
       <c r="O4" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="P4" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="Q4" t="n">
         <v>0.707</v>
       </c>
       <c r="R4" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S4" t="n">
         <v>29.6</v>
@@ -1076,7 +1143,7 @@
         <v>40.7</v>
       </c>
       <c r="U4" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="V4" t="n">
         <v>14.7</v>
@@ -1085,25 +1152,25 @@
         <v>7.5</v>
       </c>
       <c r="X4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y4" t="n">
         <v>6.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>95.7</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>-5.2</v>
+        <v>-5</v>
       </c>
       <c r="AD4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE4" t="n">
         <v>23</v>
@@ -1124,16 +1191,16 @@
         <v>19</v>
       </c>
       <c r="AK4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM4" t="n">
         <v>15</v>
       </c>
       <c r="AN4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO4" t="n">
         <v>21</v>
@@ -1148,13 +1215,13 @@
         <v>18</v>
       </c>
       <c r="AS4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT4" t="n">
         <v>24</v>
       </c>
       <c r="AU4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AV4" t="n">
         <v>18</v>
@@ -1163,7 +1230,7 @@
         <v>13</v>
       </c>
       <c r="AX4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AY4" t="n">
         <v>30</v>
@@ -1175,10 +1242,10 @@
         <v>15</v>
       </c>
       <c r="BB4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BC4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-17-2007-08</t>
+          <t>2008-03-17</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E5" t="n">
         <v>26</v>
       </c>
       <c r="F5" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G5" t="n">
-        <v>0.394</v>
+        <v>0.4</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
@@ -1225,7 +1292,7 @@
         <v>36.2</v>
       </c>
       <c r="J5" t="n">
-        <v>84.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K5" t="n">
         <v>0.429</v>
@@ -1237,37 +1304,37 @@
         <v>15.9</v>
       </c>
       <c r="N5" t="n">
-        <v>0.354</v>
+        <v>0.353</v>
       </c>
       <c r="O5" t="n">
         <v>18.6</v>
       </c>
       <c r="P5" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.746</v>
+        <v>0.747</v>
       </c>
       <c r="R5" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="S5" t="n">
         <v>30.2</v>
       </c>
       <c r="T5" t="n">
-        <v>43.6</v>
+        <v>43.7</v>
       </c>
       <c r="U5" t="n">
         <v>21.7</v>
       </c>
       <c r="V5" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W5" t="n">
         <v>7.7</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y5" t="n">
         <v>5.8</v>
@@ -1282,10 +1349,10 @@
         <v>96.59999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.7</v>
+        <v>-2.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AE5" t="n">
         <v>21</v>
@@ -1297,7 +1364,7 @@
         <v>21</v>
       </c>
       <c r="AH5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI5" t="n">
         <v>21</v>
@@ -1321,7 +1388,7 @@
         <v>16</v>
       </c>
       <c r="AP5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ5" t="n">
         <v>19</v>
@@ -1339,7 +1406,7 @@
         <v>12</v>
       </c>
       <c r="AV5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW5" t="n">
         <v>9</v>
@@ -1360,7 +1427,7 @@
         <v>19</v>
       </c>
       <c r="BC5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-17-2007-08</t>
+          <t>2008-03-17</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E6" t="n">
         <v>38</v>
       </c>
       <c r="F6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H6" t="n">
         <v>48.5</v>
@@ -1416,19 +1483,19 @@
         <v>7.2</v>
       </c>
       <c r="M6" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0.366</v>
+        <v>0.367</v>
       </c>
       <c r="O6" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="P6" t="n">
         <v>25.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.72</v>
+        <v>0.721</v>
       </c>
       <c r="R6" t="n">
         <v>13</v>
@@ -1440,13 +1507,13 @@
         <v>44.3</v>
       </c>
       <c r="U6" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="V6" t="n">
         <v>14.2</v>
       </c>
       <c r="W6" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X6" t="n">
         <v>5</v>
@@ -1455,16 +1522,16 @@
         <v>4.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="AA6" t="n">
         <v>20.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>97.3</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.5</v>
+        <v>-0.3</v>
       </c>
       <c r="AD6" t="n">
         <v>3</v>
@@ -1506,7 +1573,7 @@
         <v>14</v>
       </c>
       <c r="AQ6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR6" t="n">
         <v>3</v>
@@ -1533,10 +1600,10 @@
         <v>13</v>
       </c>
       <c r="AZ6" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BA6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB6" t="n">
         <v>17</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-17-2007-08</t>
+          <t>2008-03-17</t>
         </is>
       </c>
     </row>
@@ -1649,19 +1716,19 @@
         <v>5</v>
       </c>
       <c r="AD7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF7" t="n">
         <v>8</v>
       </c>
-      <c r="AF7" t="n">
-        <v>7</v>
-      </c>
       <c r="AG7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI7" t="n">
         <v>14</v>
@@ -1685,7 +1752,7 @@
         <v>8</v>
       </c>
       <c r="AP7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ7" t="n">
         <v>1</v>
@@ -1697,7 +1764,7 @@
         <v>7</v>
       </c>
       <c r="AT7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU7" t="n">
         <v>21</v>
@@ -1709,7 +1776,7 @@
         <v>29</v>
       </c>
       <c r="AX7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY7" t="n">
         <v>6</v>
@@ -1721,10 +1788,10 @@
         <v>14</v>
       </c>
       <c r="BB7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-17-2007-08</t>
+          <t>2008-03-17</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>3.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AE8" t="n">
         <v>12</v>
@@ -1843,7 +1910,7 @@
         <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AI8" t="n">
         <v>4</v>
@@ -1861,7 +1928,7 @@
         <v>13</v>
       </c>
       <c r="AN8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1885,7 +1952,7 @@
         <v>3</v>
       </c>
       <c r="AV8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW8" t="n">
         <v>2</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-17-2007-08</t>
+          <t>2008-03-17</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>7.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2025,13 +2092,13 @@
         <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI9" t="n">
         <v>17</v>
       </c>
       <c r="AJ9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK9" t="n">
         <v>13</v>
@@ -2046,7 +2113,7 @@
         <v>7</v>
       </c>
       <c r="AO9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP9" t="n">
         <v>18</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-17-2007-08</t>
+          <t>2008-03-17</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>3.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AE10" t="n">
         <v>11</v>
@@ -2216,22 +2283,22 @@
         <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM10" t="n">
         <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO10" t="n">
         <v>15</v>
       </c>
       <c r="AP10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ10" t="n">
         <v>18</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-17-2007-08</t>
+          <t>2008-03-17</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>5.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AE11" t="n">
         <v>3</v>
@@ -2389,7 +2456,7 @@
         <v>3</v>
       </c>
       <c r="AH11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI11" t="n">
         <v>13</v>
@@ -2419,7 +2486,7 @@
         <v>26</v>
       </c>
       <c r="AR11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS11" t="n">
         <v>4</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-17-2007-08</t>
+          <t>2008-03-17</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F12" t="n">
         <v>41</v>
       </c>
       <c r="G12" t="n">
-        <v>0.388</v>
+        <v>0.379</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
       </c>
       <c r="I12" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J12" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="K12" t="n">
         <v>0.441</v>
@@ -2511,7 +2578,7 @@
         <v>24.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0.364</v>
+        <v>0.366</v>
       </c>
       <c r="O12" t="n">
         <v>18.8</v>
@@ -2520,16 +2587,16 @@
         <v>24.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.768</v>
+        <v>0.767</v>
       </c>
       <c r="R12" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S12" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="T12" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="U12" t="n">
         <v>22.6</v>
@@ -2541,7 +2608,7 @@
         <v>7.6</v>
       </c>
       <c r="X12" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y12" t="n">
         <v>5.1</v>
@@ -2553,16 +2620,16 @@
         <v>21.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.2</v>
+        <v>103.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2.6</v>
+        <v>-2.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF12" t="n">
         <v>22</v>
@@ -2571,7 +2638,7 @@
         <v>22</v>
       </c>
       <c r="AH12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI12" t="n">
         <v>9</v>
@@ -2589,7 +2656,7 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO12" t="n">
         <v>14</v>
@@ -2607,19 +2674,19 @@
         <v>8</v>
       </c>
       <c r="AT12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV12" t="n">
         <v>27</v>
       </c>
       <c r="AW12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY12" t="n">
         <v>22</v>
@@ -2634,7 +2701,7 @@
         <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-17-2007-08</t>
+          <t>2008-03-17</t>
         </is>
       </c>
     </row>
@@ -2663,85 +2730,85 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E13" t="n">
         <v>21</v>
       </c>
       <c r="F13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G13" t="n">
-        <v>0.318</v>
+        <v>0.323</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
       </c>
       <c r="I13" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="J13" t="n">
-        <v>78.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.436</v>
+        <v>0.437</v>
       </c>
       <c r="L13" t="n">
         <v>4.3</v>
       </c>
       <c r="M13" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="N13" t="n">
-        <v>0.329</v>
+        <v>0.332</v>
       </c>
       <c r="O13" t="n">
         <v>21</v>
       </c>
       <c r="P13" t="n">
-        <v>26.7</v>
+        <v>26.6</v>
       </c>
       <c r="Q13" t="n">
         <v>0.787</v>
       </c>
       <c r="R13" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="S13" t="n">
         <v>30.5</v>
       </c>
       <c r="T13" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
       <c r="U13" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V13" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W13" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X13" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y13" t="n">
         <v>5</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AA13" t="n">
         <v>21.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>94</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AC13" t="n">
         <v>-6.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
@@ -2753,7 +2820,7 @@
         <v>25</v>
       </c>
       <c r="AH13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI13" t="n">
         <v>29</v>
@@ -2762,7 +2829,7 @@
         <v>25</v>
       </c>
       <c r="AK13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL13" t="n">
         <v>28</v>
@@ -2774,7 +2841,7 @@
         <v>29</v>
       </c>
       <c r="AO13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP13" t="n">
         <v>9</v>
@@ -2801,13 +2868,13 @@
         <v>20</v>
       </c>
       <c r="AX13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY13" t="n">
         <v>18</v>
       </c>
       <c r="AZ13" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA13" t="n">
         <v>9</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-17-2007-08</t>
+          <t>2008-03-17</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>7</v>
       </c>
       <c r="AD14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AE14" t="n">
         <v>4</v>
@@ -2935,7 +3002,7 @@
         <v>4</v>
       </c>
       <c r="AH14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-17-2007-08</t>
+          <t>2008-03-17</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F15" t="n">
         <v>50</v>
       </c>
       <c r="G15" t="n">
-        <v>0.242</v>
+        <v>0.231</v>
       </c>
       <c r="H15" t="n">
         <v>48.3</v>
@@ -3054,7 +3121,7 @@
         <v>7.5</v>
       </c>
       <c r="M15" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="N15" t="n">
         <v>0.351</v>
@@ -3063,34 +3130,34 @@
         <v>18.3</v>
       </c>
       <c r="P15" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.731</v>
+        <v>0.734</v>
       </c>
       <c r="R15" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="S15" t="n">
         <v>30.9</v>
       </c>
       <c r="T15" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="U15" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="V15" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="W15" t="n">
         <v>6.2</v>
       </c>
       <c r="X15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y15" t="n">
         <v>4.8</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>4.9</v>
       </c>
       <c r="Z15" t="n">
         <v>19.5</v>
@@ -3102,19 +3169,19 @@
         <v>99.40000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.5</v>
+        <v>-6.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AE15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF15" t="n">
         <v>27</v>
       </c>
       <c r="AG15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH15" t="n">
         <v>15</v>
@@ -3135,7 +3202,7 @@
         <v>5</v>
       </c>
       <c r="AN15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO15" t="n">
         <v>19</v>
@@ -3153,7 +3220,7 @@
         <v>12</v>
       </c>
       <c r="AT15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU15" t="n">
         <v>27</v>
@@ -3162,10 +3229,10 @@
         <v>28</v>
       </c>
       <c r="AW15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX15" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AY15" t="n">
         <v>16</v>
@@ -3180,7 +3247,7 @@
         <v>13</v>
       </c>
       <c r="BC15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-17-2007-08</t>
+          <t>2008-03-17</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-7.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -3326,7 +3393,7 @@
         <v>21</v>
       </c>
       <c r="AQ16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR16" t="n">
         <v>29</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-17-2007-08</t>
+          <t>2008-03-17</t>
         </is>
       </c>
     </row>
@@ -3469,19 +3536,19 @@
         <v>-6.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AE17" t="n">
         <v>24</v>
       </c>
       <c r="AF17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG17" t="n">
         <v>24</v>
       </c>
       <c r="AH17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI17" t="n">
         <v>18</v>
@@ -3520,7 +3587,7 @@
         <v>23</v>
       </c>
       <c r="AU17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV17" t="n">
         <v>14</v>
@@ -3535,7 +3602,7 @@
         <v>19</v>
       </c>
       <c r="AZ17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA17" t="n">
         <v>19</v>
@@ -3544,7 +3611,7 @@
         <v>22</v>
       </c>
       <c r="BC17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-17-2007-08</t>
+          <t>2008-03-17</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F18" t="n">
         <v>50</v>
       </c>
       <c r="G18" t="n">
-        <v>0.242</v>
+        <v>0.231</v>
       </c>
       <c r="H18" t="n">
         <v>48.1</v>
@@ -3591,25 +3658,25 @@
         <v>37</v>
       </c>
       <c r="J18" t="n">
-        <v>82.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.447</v>
+        <v>0.446</v>
       </c>
       <c r="L18" t="n">
         <v>5.3</v>
       </c>
       <c r="M18" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0.341</v>
+        <v>0.34</v>
       </c>
       <c r="O18" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="P18" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="Q18" t="n">
         <v>0.728</v>
@@ -3618,13 +3685,13 @@
         <v>12</v>
       </c>
       <c r="S18" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="T18" t="n">
         <v>41.4</v>
       </c>
       <c r="U18" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="V18" t="n">
         <v>15.1</v>
@@ -3633,7 +3700,7 @@
         <v>7.6</v>
       </c>
       <c r="X18" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y18" t="n">
         <v>5.9</v>
@@ -3645,22 +3712,22 @@
         <v>17.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>94.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>-7</v>
+        <v>-7.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AE18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF18" t="n">
         <v>27</v>
       </c>
       <c r="AG18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH18" t="n">
         <v>28</v>
@@ -3705,10 +3772,10 @@
         <v>26</v>
       </c>
       <c r="AV18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX18" t="n">
         <v>29</v>
@@ -3723,7 +3790,7 @@
         <v>30</v>
       </c>
       <c r="BB18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC18" t="n">
         <v>28</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-17-2007-08</t>
+          <t>2008-03-17</t>
         </is>
       </c>
     </row>
@@ -3833,19 +3900,19 @@
         <v>-5.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AE19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF19" t="n">
         <v>19</v>
       </c>
       <c r="AG19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH19" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3854,10 +3921,10 @@
         <v>28</v>
       </c>
       <c r="AK19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM19" t="n">
         <v>19</v>
@@ -3884,10 +3951,10 @@
         <v>11</v>
       </c>
       <c r="AU19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW19" t="n">
         <v>23</v>
@@ -3896,7 +3963,7 @@
         <v>17</v>
       </c>
       <c r="AY19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ19" t="n">
         <v>26</v>
@@ -3905,10 +3972,10 @@
         <v>8</v>
       </c>
       <c r="BB19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-17-2007-08</t>
+          <t>2008-03-17</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F20" t="n">
         <v>21</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.677</v>
       </c>
       <c r="H20" t="n">
         <v>48.4</v>
@@ -3970,10 +4037,10 @@
         <v>0.39</v>
       </c>
       <c r="O20" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="P20" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="Q20" t="n">
         <v>0.77</v>
@@ -3982,16 +4049,16 @@
         <v>11.8</v>
       </c>
       <c r="S20" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="T20" t="n">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="U20" t="n">
         <v>21.7</v>
       </c>
       <c r="V20" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="W20" t="n">
         <v>7.5</v>
@@ -4003,31 +4070,31 @@
         <v>4.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="AA20" t="n">
         <v>18.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>100.3</v>
+        <v>100.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AD20" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AE20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF20" t="n">
         <v>4</v>
       </c>
       <c r="AG20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI20" t="n">
         <v>6</v>
@@ -4036,7 +4103,7 @@
         <v>7</v>
       </c>
       <c r="AK20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL20" t="n">
         <v>5</v>
@@ -4066,7 +4133,7 @@
         <v>9</v>
       </c>
       <c r="AU20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV20" t="n">
         <v>3</v>
@@ -4078,7 +4145,7 @@
         <v>28</v>
       </c>
       <c r="AY20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ20" t="n">
         <v>1</v>
@@ -4090,7 +4157,7 @@
         <v>12</v>
       </c>
       <c r="BC20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-17-2007-08</t>
+          <t>2008-03-17</t>
         </is>
       </c>
     </row>
@@ -4119,19 +4186,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E21" t="n">
         <v>19</v>
       </c>
       <c r="F21" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G21" t="n">
-        <v>0.284</v>
+        <v>0.288</v>
       </c>
       <c r="H21" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I21" t="n">
         <v>35.3</v>
@@ -4140,52 +4207,52 @@
         <v>80.5</v>
       </c>
       <c r="K21" t="n">
-        <v>0.438</v>
+        <v>0.439</v>
       </c>
       <c r="L21" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="M21" t="n">
         <v>17.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0.336</v>
+        <v>0.333</v>
       </c>
       <c r="O21" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="P21" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.724</v>
+        <v>0.725</v>
       </c>
       <c r="R21" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="S21" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="T21" t="n">
-        <v>41.9</v>
+        <v>41.7</v>
       </c>
       <c r="U21" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="V21" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W21" t="n">
         <v>6.1</v>
       </c>
       <c r="X21" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Y21" t="n">
         <v>5.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AA21" t="n">
         <v>21</v>
@@ -4194,10 +4261,10 @@
         <v>95.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>-6.7</v>
+        <v>-6.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE21" t="n">
         <v>26</v>
@@ -4215,7 +4282,7 @@
         <v>28</v>
       </c>
       <c r="AJ21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK21" t="n">
         <v>27</v>
@@ -4224,25 +4291,25 @@
         <v>20</v>
       </c>
       <c r="AM21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN21" t="n">
         <v>28</v>
       </c>
       <c r="AO21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP21" t="n">
         <v>10</v>
       </c>
       <c r="AQ21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT21" t="n">
         <v>16</v>
@@ -4254,16 +4321,16 @@
         <v>19</v>
       </c>
       <c r="AW21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA21" t="n">
         <v>16</v>
@@ -4272,7 +4339,7 @@
         <v>26</v>
       </c>
       <c r="BC21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-17-2007-08</t>
+          <t>2008-03-17</t>
         </is>
       </c>
     </row>
@@ -4301,52 +4368,52 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E22" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F22" t="n">
         <v>24</v>
       </c>
       <c r="G22" t="n">
-        <v>0.652</v>
+        <v>0.647</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
       </c>
       <c r="I22" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="J22" t="n">
-        <v>78.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.475</v>
+        <v>0.477</v>
       </c>
       <c r="L22" t="n">
         <v>9.5</v>
       </c>
       <c r="M22" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="N22" t="n">
-        <v>0.383</v>
+        <v>0.382</v>
       </c>
       <c r="O22" t="n">
         <v>20.8</v>
       </c>
       <c r="P22" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.725</v>
+        <v>0.724</v>
       </c>
       <c r="R22" t="n">
         <v>9.5</v>
       </c>
       <c r="S22" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="T22" t="n">
         <v>42.1</v>
@@ -4355,10 +4422,10 @@
         <v>20.4</v>
       </c>
       <c r="V22" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W22" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="X22" t="n">
         <v>4.2</v>
@@ -4376,13 +4443,13 @@
         <v>105</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AD22" t="n">
         <v>1</v>
       </c>
       <c r="AE22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF22" t="n">
         <v>9</v>
@@ -4397,13 +4464,13 @@
         <v>10</v>
       </c>
       <c r="AJ22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK22" t="n">
         <v>5</v>
       </c>
       <c r="AL22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM22" t="n">
         <v>2</v>
@@ -4418,7 +4485,7 @@
         <v>3</v>
       </c>
       <c r="AQ22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR22" t="n">
         <v>28</v>
@@ -4436,7 +4503,7 @@
         <v>13</v>
       </c>
       <c r="AW22" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AX22" t="n">
         <v>24</v>
@@ -4454,7 +4521,7 @@
         <v>6</v>
       </c>
       <c r="BC22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-17-2007-08</t>
+          <t>2008-03-17</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>0.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE23" t="n">
         <v>16</v>
@@ -4573,7 +4640,7 @@
         <v>17</v>
       </c>
       <c r="AH23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI23" t="n">
         <v>11</v>
@@ -4609,7 +4676,7 @@
         <v>28</v>
       </c>
       <c r="AT23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU23" t="n">
         <v>24</v>
@@ -4621,7 +4688,7 @@
         <v>5</v>
       </c>
       <c r="AX23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY23" t="n">
         <v>17</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-17-2007-08</t>
+          <t>2008-03-17</t>
         </is>
       </c>
     </row>
@@ -4743,10 +4810,10 @@
         <v>4.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AE24" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AF24" t="n">
         <v>6</v>
@@ -4764,7 +4831,7 @@
         <v>6</v>
       </c>
       <c r="AK24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL24" t="n">
         <v>4</v>
@@ -4818,7 +4885,7 @@
         <v>2</v>
       </c>
       <c r="BC24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-17-2007-08</t>
+          <t>2008-03-17</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-0.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
         <v>14</v>
@@ -4949,10 +5016,10 @@
         <v>17</v>
       </c>
       <c r="AL25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN25" t="n">
         <v>6</v>
@@ -4964,19 +5031,19 @@
         <v>24</v>
       </c>
       <c r="AQ25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR25" t="n">
         <v>21</v>
       </c>
       <c r="AS25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT25" t="n">
         <v>26</v>
       </c>
       <c r="AU25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV25" t="n">
         <v>6</v>
@@ -4997,7 +5064,7 @@
         <v>21</v>
       </c>
       <c r="BB25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC25" t="n">
         <v>17</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-17-2007-08</t>
+          <t>2008-03-17</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-2.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AE26" t="n">
         <v>18</v>
@@ -5119,7 +5186,7 @@
         <v>18</v>
       </c>
       <c r="AH26" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AI26" t="n">
         <v>16</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-17-2007-08</t>
+          <t>2008-03-17</t>
         </is>
       </c>
     </row>
@@ -5211,25 +5278,25 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E27" t="n">
         <v>44</v>
       </c>
       <c r="F27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G27" t="n">
-        <v>0.657</v>
+        <v>0.667</v>
       </c>
       <c r="H27" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
       <c r="I27" t="n">
-        <v>35.6</v>
+        <v>35.7</v>
       </c>
       <c r="J27" t="n">
-        <v>78.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="K27" t="n">
         <v>0.454</v>
@@ -5250,19 +5317,19 @@
         <v>22</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.76</v>
+        <v>0.758</v>
       </c>
       <c r="R27" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="S27" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="T27" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="U27" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V27" t="n">
         <v>12.8</v>
@@ -5271,7 +5338,7 @@
         <v>6.6</v>
       </c>
       <c r="X27" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Y27" t="n">
         <v>4.4</v>
@@ -5280,34 +5347,34 @@
         <v>19</v>
       </c>
       <c r="AA27" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AB27" t="n">
-        <v>95.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE27" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AF27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH27" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI27" t="n">
         <v>25</v>
       </c>
       <c r="AJ27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK27" t="n">
         <v>15</v>
@@ -5328,10 +5395,10 @@
         <v>27</v>
       </c>
       <c r="AQ27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS27" t="n">
         <v>10</v>
@@ -5352,7 +5419,7 @@
         <v>26</v>
       </c>
       <c r="AY27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ27" t="n">
         <v>2</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-17-2007-08</t>
+          <t>2008-03-17</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE28" t="n">
         <v>27</v>
@@ -5480,7 +5547,7 @@
         <v>29</v>
       </c>
       <c r="AG28" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AH28" t="n">
         <v>17</v>
@@ -5510,7 +5577,7 @@
         <v>25</v>
       </c>
       <c r="AQ28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR28" t="n">
         <v>11</v>
@@ -5522,7 +5589,7 @@
         <v>1</v>
       </c>
       <c r="AU28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV28" t="n">
         <v>30</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-17-2007-08</t>
+          <t>2008-03-17</t>
         </is>
       </c>
     </row>
@@ -5575,43 +5642,43 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E29" t="n">
         <v>34</v>
       </c>
       <c r="F29" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G29" t="n">
-        <v>0.507</v>
+        <v>0.515</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
       </c>
       <c r="I29" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="J29" t="n">
         <v>82.09999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>0.466</v>
+        <v>0.467</v>
       </c>
       <c r="L29" t="n">
         <v>7.3</v>
       </c>
       <c r="M29" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="N29" t="n">
         <v>0.404</v>
       </c>
       <c r="O29" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="P29" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="Q29" t="n">
         <v>0.8120000000000001</v>
@@ -5623,22 +5690,22 @@
         <v>30.4</v>
       </c>
       <c r="T29" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="U29" t="n">
         <v>23.3</v>
       </c>
       <c r="V29" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="W29" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X29" t="n">
         <v>4</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z29" t="n">
         <v>19.9</v>
@@ -5647,25 +5714,25 @@
         <v>18.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>100.3</v>
+        <v>100.7</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE29" t="n">
         <v>15</v>
       </c>
       <c r="AF29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG29" t="n">
         <v>15</v>
       </c>
       <c r="AH29" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AI29" t="n">
         <v>7</v>
@@ -5686,7 +5753,7 @@
         <v>1</v>
       </c>
       <c r="AO29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP29" t="n">
         <v>29</v>
@@ -5695,7 +5762,7 @@
         <v>2</v>
       </c>
       <c r="AR29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS29" t="n">
         <v>16</v>
@@ -5704,7 +5771,7 @@
         <v>28</v>
       </c>
       <c r="AU29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV29" t="n">
         <v>2</v>
@@ -5713,7 +5780,7 @@
         <v>19</v>
       </c>
       <c r="AX29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY29" t="n">
         <v>5</v>
@@ -5725,7 +5792,7 @@
         <v>29</v>
       </c>
       <c r="BB29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC29" t="n">
         <v>13</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-17-2007-08</t>
+          <t>2008-03-17</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E30" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F30" t="n">
         <v>24</v>
       </c>
       <c r="G30" t="n">
-        <v>0.652</v>
+        <v>0.647</v>
       </c>
       <c r="H30" t="n">
         <v>48.1</v>
@@ -5775,31 +5842,31 @@
         <v>39.9</v>
       </c>
       <c r="J30" t="n">
-        <v>80.3</v>
+        <v>80.5</v>
       </c>
       <c r="K30" t="n">
-        <v>0.497</v>
+        <v>0.496</v>
       </c>
       <c r="L30" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="M30" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="N30" t="n">
-        <v>0.371</v>
+        <v>0.368</v>
       </c>
       <c r="O30" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="P30" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.758</v>
+        <v>0.76</v>
       </c>
       <c r="R30" t="n">
-        <v>11.2</v>
+        <v>11.4</v>
       </c>
       <c r="S30" t="n">
         <v>29.3</v>
@@ -5808,7 +5875,7 @@
         <v>40.6</v>
       </c>
       <c r="U30" t="n">
-        <v>26.3</v>
+        <v>26.4</v>
       </c>
       <c r="V30" t="n">
         <v>14.9</v>
@@ -5823,22 +5890,22 @@
         <v>5.4</v>
       </c>
       <c r="Z30" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="AA30" t="n">
         <v>23.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>106.3</v>
+        <v>106.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF30" t="n">
         <v>9</v>
@@ -5853,10 +5920,10 @@
         <v>3</v>
       </c>
       <c r="AJ30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL30" t="n">
         <v>26</v>
@@ -5874,7 +5941,7 @@
         <v>2</v>
       </c>
       <c r="AQ30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR30" t="n">
         <v>16</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-17-2007-08</t>
+          <t>2008-03-17</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E31" t="n">
         <v>33</v>
       </c>
       <c r="F31" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5</v>
+        <v>0.508</v>
       </c>
       <c r="H31" t="n">
         <v>48.6</v>
@@ -5981,13 +6048,13 @@
         <v>0.79</v>
       </c>
       <c r="R31" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="S31" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="T31" t="n">
-        <v>41.9</v>
+        <v>42.1</v>
       </c>
       <c r="U31" t="n">
         <v>19.2</v>
@@ -5999,31 +6066,31 @@
         <v>7.9</v>
       </c>
       <c r="X31" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y31" t="n">
         <v>4.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AA31" t="n">
         <v>20.4</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AE31" t="n">
         <v>16</v>
       </c>
       <c r="AF31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG31" t="n">
         <v>16</v>
@@ -6062,10 +6129,10 @@
         <v>6</v>
       </c>
       <c r="AS31" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AT31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU31" t="n">
         <v>28</v>
@@ -6077,7 +6144,7 @@
         <v>7</v>
       </c>
       <c r="AX31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY31" t="n">
         <v>10</v>
@@ -6086,7 +6153,7 @@
         <v>5</v>
       </c>
       <c r="BA31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB31" t="n">
         <v>14</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-17-2007-08</t>
+          <t>2008-03-17</t>
         </is>
       </c>
     </row>
